--- a/human_validation/judge/kor/judge_D023_S002_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S002_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,418 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 건요, 그렇게 먹은 밤이 지나고 나면 부스러기랑 빈 그릇들에 둘러싸여 앉아 있게 되는데, 그럴 때마다 제 자신이 너무 부끄럽고 혐오스러워요. 어떨 때는 정말 심해서 기도도 제대로 못 하고, 다음 날 아침에 교회 사람들 얼굴도 제대로 못 봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 그런 밤에 먹는 걸 스스로 통제하고 있다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 통제가 안 돼요. 집이 조용해지고 첫 입을 베어 무는 순간, 제 이성이 그냥 한 발짝 물러나 버리는 것 같아요. 속으로 “Belinda, 이제 그만해”라고 계속 말하는데도, 손은 그냥 계속 더 집어 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 말씀하신 것처럼 통제력을 잃은 느낌이 드는 그런 식사가 항상 밤에만 일어나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 제가 가장 많이 알아차리는 건 밤에, 모든 게 조용해진 후인데, 항상 그때만 그런지는 제대로 기록해본 적이 없어서 확실히는 말씀드리기 어려워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이런 일들 때문에 시간이 지나면서 체중에 눈에 띄는 변화가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 몇 년 동안 체중이 오르락내리락하긴 했는데, 그게 그런 폭식하는 밤들 때문인지는 확실히 말씀드리기 어려워요. 자세히 기록해두지는 않았거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 그런 밤에는, 비슷한 시간 동안 평소보다 훨씬 많은 양을 드신다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 심한 밤에는 평소보다 훨씬 많이 먹어요. 남은 캐서롤 한 접시로 시작했다가, 어느새 브라우니 팬 절반이랑 비스킷 몇 개, 냉장고에 있는 치킨 샐러드까지 한자리에서 다 먹어버려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이렇게 드신 후에 보통 죄책감을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 아주 심한 죄책감이요. 끝나고 나면 부스러기랑 빈 그릇에 둘러싸여 앉아서, 제 자신이 부끄럽고 혐오스러워요. 어떨 때는 다음 날 아침에 기도도 제대로 못 하고, 교회 사람들 얼굴도 제대로 못 봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 이렇게 드시는 동안, 평소에 즐기던 다른 일들에는 흥미가 없어지시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 그러는 중에는 다른 일은 별로 생각 안 해요. 그때는 거의 먹는 것에만 집중하게 되는데, 평소 하던 일들에 흥미를 잃었다고 딱 잘라 말하기는 어려울 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 그럴 때 정말 빠르게 드신다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 그래요. 어떨 때는 그냥 부엌 조리대에 선 채로 너무 빨리 먹어서 파운드케이크나 크래커 같은 걸 먹으면서도 맛도 잘 못 느껴요. 제대로 씹지도 않고 삼키고 있는 저를 발견하기도 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 이런 일 후에 배가 아프거나 속이 메스꺼운 것 같은 신체 증상을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네. 배가 아플 정도로 불러요. 배가 팽팽하고 아파서, 잠옷 아래로도 배가 눌리는 게 느껴질 정도예요. 움직이면 아파서 리클라이너에 조심스럽게 앉아야 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 그럴 때 만약 다른 선택지가 있었다면, 다른 걸 하고 싶으셨을 것 같으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 그 순간에는 “차라리 다른 걸 하고 싶다”는 생각은 안 해요. 그냥 먹는 데 빠져있는 것 같아요. 뭔가가 끼어들면 멈출 수 있을지도 모르지만, 그런 식으로는 딱히 느껴본 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 그렇게 드시는 동안 다른 일을 생각하거나 하고 싶다는 마음이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 그럴 때는 거의 음식에만 집중해요. 다른 걸 하고 싶다고 바라면서 앉아 있는 것 같지는 않아요. 그보다는 멈출 때까지 거기에 갇혀 있는 느낌에 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 이렇게 드시는 걸 보통 숨기거나 비밀로 하려고 하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네... 그래요. 브릿지 모임이나 교회 저녁 식사에서는 다른 사람들처럼 점잖게 보이는 작은 접시를 들어요. 근데 나중에 사람들이 떠나고 나면, 다시 부엌으로 가서 아무도 안 보는 데서 남은 음식을 먹어요. 창피해서, 그 부분은 숨기려고 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 그런 식사를 하는 동안 다른 할 일이 있었다면, 그걸 하고 싶으셨을 것 같으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 시작될 때는 다른 뭘 할 수 있는지 딱히 생각 안 해요. 바로 옆에 뭔가 있었다면 모를까, 그 순간에 그걸 원하는 저 자신을 딱히 느껴본 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 이렇게 통제력을 잃은 느낌이 드는 식사가 규칙적으로 일어나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네. 친구가 세상을 떠난 후로는 꽤 규칙적으로 일어나고 있어요... 주로 밤늦게요. 거의 매주 적어도 한두 번은 되는 것 같고, 완전히 멈추거나 나아진 달은 없었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 보통 스트레스를 받거나 불안하거나 뭔가로 속상할 때 이렇게 드시기 시작하는 것 같으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 확실히는 모르겠어요. 가끔 속상할 때도 있긴 한데, 그게 매번 시작하는 원인인지는 자세히 살펴본 적이 없어요. 그냥 어쩌다 보니 그렇게 되고, 그러면 그 안에 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 이런 일이 시작되기 직전에 보통 속상하거나 감정이 격해지시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 시작되기 직전에 뚜렷한 감정을 느낀 적은 없는 것 같아요. 가끔은 속상할 수도 있지만, 다른 때는 그냥 그렇게 되고 이미 먹고 있을 때까지 별생각이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 이런 식사가 보통 속상함이나 감정적인 상태 때문에 촉발된다고 생각하세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 확실히는 말씀드리기 어려워요. 가끔 속상할 때 그럴 수 있다는 건 아는데, 그게 매번 있는 계기라고는 느껴본 적이 없어요. 어떨 때는 이미 그러고 있을 때까지 제가 뭘 느끼고 있는지도 모를 때가 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 이럴 때 본인이 뭘 먹고 있는지, 맛이 어떤지 제대로 인식하지 못한다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네. 대부분은 너무 빨리 먹어서 맛을 제대로 못 느껴요. 부엌 조리대에 서서 파운드케이크나 크래커를 먹으면서 그냥 계속 먹어요. 어떨 때는 제대로 씹지도 않고 삼키고 있는 저를 발견해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 혹시 먹고 있는 동안에는 스스로를 비난하거나 나쁘게 느끼지 않다가, 끝나고 나서야 그런 기분이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 네. 하고 있는 동안에는 아직 제 자신에 대해 나쁜 생각은 별로 안 해요. 끝나고 주변을 둘러보고 부스러기랑 빈 그릇을 보게 될 때, 그때 확 밀려와요. 너무 부끄럽고 제 자신이 혐오스러워요. 그러고 나서 어떤 아침에는 기도도 제대로 못 하고 교회 사람들 얼굴도 제대로 못 봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 폭식장애 (D023) | 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>진단명: 폭식장애 (D023)
 인구통계: 성별 여성 / 나이 65 / 직업상태 not in workforce / 최종학력 고등학교 졸업
@@ -575,476 +978,41 @@
 증상 지속 기간: 5 months
 추가 요건: The binge eating occurs, on average, at least once a week for 3 months
 주호소 증상 코드: S055
-배경 서술: Belinda의 가장 가까운 브릿지 파트너이자 오랜 교회 친구가 갑작스럽게 세상을 떠나면서, 그는 추모 오찬을 준비하는 걸 돕고 커뮤니티 센터의 여러 업무를 맡게 되었으며, 한때 전화 통화와 퀼트 계획, 대회 뒷담화로 채워졌던 저녁 시간을 홀로 마주하게 되었다. 그 후 5개월 동안 그는 집에 여분의 구운 빵과 포트럭 남은 음식을 쟁여두기 시작했고, 이내 밤늦게 혼자 유난히 많은 양을 빠르게 먹어서 배가 아플 정도로 부르고, 그 후 깊은 죄책감을 느끼는 일이 반복되었다. 그가 속한 남부 교회 공동체에서는 환대와 절제가 매우 중요했기 때문에, 그는 대외적으로 보이는 유능한 모습과 사적인 폭식 사이의 괴리에 점점 더 비밀스러워지고 괴로워하게 되었다. 노인복지관에서 열린 섭식 문제에 관한 건강 강연을 듣고 이것이 더 이상 평범한 애도로 인한 식습관이 아니라는 걸 깨달은 후, 그는 스스로 정신건강의학과 진료를 받기로 했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 건요, 그렇게 먹은 밤이 지나고 나면 부스러기랑 빈 그릇들에 둘러싸여 앉아 있게 되는데, 그럴 때마다 제 자신이 너무 부끄럽고 혐오스러워요. 어떨 때는 정말 심해서 기도도 제대로 못 하고, 다음 날 아침에 교회 사람들 얼굴도 제대로 못 봐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 그런 밤에 먹는 걸 스스로 통제하고 있다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 통제가 안 돼요. 집이 조용해지고 첫 입을 베어 무는 순간, 제 이성이 그냥 한 발짝 물러나 버리는 것 같아요. 속으로 “Belinda, 이제 그만해”라고 계속 말하는데도, 손은 그냥 계속 더 집어 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 말씀하신 것처럼 통제력을 잃은 느낌이 드는 그런 식사가 항상 밤에만 일어나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 제가 가장 많이 알아차리는 건 밤에, 모든 게 조용해진 후인데, 항상 그때만 그런지는 제대로 기록해본 적이 없어서 확실히는 말씀드리기 어려워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이런 일들 때문에 시간이 지나면서 체중에 눈에 띄는 변화가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 몇 년 동안 체중이 오르락내리락하긴 했는데, 그게 그런 폭식하는 밤들 때문인지는 확실히 말씀드리기 어려워요. 자세히 기록해두지는 않았거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 그런 밤에는, 비슷한 시간 동안 평소보다 훨씬 많은 양을 드신다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 심한 밤에는 평소보다 훨씬 많이 먹어요. 남은 캐서롤 한 접시로 시작했다가, 어느새 브라우니 팬 절반이랑 비스킷 몇 개, 냉장고에 있는 치킨 샐러드까지 한자리에서 다 먹어버려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이렇게 드신 후에 보통 죄책감을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 아주 심한 죄책감이요. 끝나고 나면 부스러기랑 빈 그릇에 둘러싸여 앉아서, 제 자신이 부끄럽고 혐오스러워요. 어떨 때는 다음 날 아침에 기도도 제대로 못 하고, 교회 사람들 얼굴도 제대로 못 봐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 이렇게 드시는 동안, 평소에 즐기던 다른 일들에는 흥미가 없어지시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 그러는 중에는 다른 일은 별로 생각 안 해요. 그때는 거의 먹는 것에만 집중하게 되는데, 평소 하던 일들에 흥미를 잃었다고 딱 잘라 말하기는 어려울 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 그럴 때 정말 빠르게 드신다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 그래요. 어떨 때는 그냥 부엌 조리대에 선 채로 너무 빨리 먹어서 파운드케이크나 크래커 같은 걸 먹으면서도 맛도 잘 못 느껴요. 제대로 씹지도 않고 삼키고 있는 저를 발견하기도 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 이런 일 후에 배가 아프거나 속이 메스꺼운 것 같은 신체 증상을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네. 배가 아플 정도로 불러요. 배가 팽팽하고 아파서, 잠옷 아래로도 배가 눌리는 게 느껴질 정도예요. 움직이면 아파서 리클라이너에 조심스럽게 앉아야 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 그럴 때 만약 다른 선택지가 있었다면, 다른 걸 하고 싶으셨을 것 같으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 그 순간에는 “차라리 다른 걸 하고 싶다”는 생각은 안 해요. 그냥 먹는 데 빠져있는 것 같아요. 뭔가가 끼어들면 멈출 수 있을지도 모르지만, 그런 식으로는 딱히 느껴본 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 그렇게 드시는 동안 다른 일을 생각하거나 하고 싶다는 마음이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 그럴 때는 거의 음식에만 집중해요. 다른 걸 하고 싶다고 바라면서 앉아 있는 것 같지는 않아요. 그보다는 멈출 때까지 거기에 갇혀 있는 느낌에 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 이렇게 드시는 걸 보통 숨기거나 비밀로 하려고 하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네... 그래요. 브릿지 모임이나 교회 저녁 식사에서는 다른 사람들처럼 점잖게 보이는 작은 접시를 들어요. 근데 나중에 사람들이 떠나고 나면, 다시 부엌으로 가서 아무도 안 보는 데서 남은 음식을 먹어요. 창피해서, 그 부분은 숨기려고 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 그런 식사를 하는 동안 다른 할 일이 있었다면, 그걸 하고 싶으셨을 것 같으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 시작될 때는 다른 뭘 할 수 있는지 딱히 생각 안 해요. 바로 옆에 뭔가 있었다면 모를까, 그 순간에 그걸 원하는 저 자신을 딱히 느껴본 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 이렇게 통제력을 잃은 느낌이 드는 식사가 규칙적으로 일어나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네. 친구가 세상을 떠난 후로는 꽤 규칙적으로 일어나고 있어요... 주로 밤늦게요. 거의 매주 적어도 한두 번은 되는 것 같고, 완전히 멈추거나 나아진 달은 없었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 보통 스트레스를 받거나 불안하거나 뭔가로 속상할 때 이렇게 드시기 시작하는 것 같으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 확실히는 모르겠어요. 가끔 속상할 때도 있긴 한데, 그게 매번 시작하는 원인인지는 자세히 살펴본 적이 없어요. 그냥 어쩌다 보니 그렇게 되고, 그러면 그 안에 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 이런 일이 시작되기 직전에 보통 속상하거나 감정이 격해지시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 시작되기 직전에 뚜렷한 감정을 느낀 적은 없는 것 같아요. 가끔은 속상할 수도 있지만, 다른 때는 그냥 그렇게 되고 이미 먹고 있을 때까지 별생각이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 이런 식사가 보통 속상함이나 감정적인 상태 때문에 촉발된다고 생각하세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 확실히는 말씀드리기 어려워요. 가끔 속상할 때 그럴 수 있다는 건 아는데, 그게 매번 있는 계기라고는 느껴본 적이 없어요. 어떨 때는 이미 그러고 있을 때까지 제가 뭘 느끼고 있는지도 모를 때가 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 이럴 때 본인이 뭘 먹고 있는지, 맛이 어떤지 제대로 인식하지 못한다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네. 대부분은 너무 빨리 먹어서 맛을 제대로 못 느껴요. 부엌 조리대에 서서 파운드케이크나 크래커를 먹으면서 그냥 계속 먹어요. 어떨 때는 제대로 씹지도 않고 삼키고 있는 저를 발견해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 혹시 먹고 있는 동안에는 스스로를 비난하거나 나쁘게 느끼지 않다가, 끝나고 나서야 그런 기분이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 네. 하고 있는 동안에는 아직 제 자신에 대해 나쁜 생각은 별로 안 해요. 끝나고 주변을 둘러보고 부스러기랑 빈 그릇을 보게 될 때, 그때 확 밀려와요. 너무 부끄럽고 제 자신이 혐오스러워요. 그러고 나서 어떤 아침에는 기도도 제대로 못 하고 교회 사람들 얼굴도 제대로 못 봐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
+배경 서술: Belinda의 가장 가까운 브릿지 파트너이자 오랜 교회 친구가 갑작스럽게 세상을 떠나면서, 그는 추모 오찬을 준비하는 걸 돕고 커뮤니티 센터의 여러 업무를 맡게 되었으며, 한때 전화 통화와 퀼트 계획, 대회 뒷담화로 채워졌던 저녁 시간을 홀로 마주하게 되었다. 그 후 5개월 동안 그는 집에 여분의 구운 빵과 포트럭 남은 음식을 쟁여두기 시작했고, 이내 밤늦게 혼자 유난히 많은 양을 빠르게 먹어서 배가 아플 정도로 부르고, 그 후 깊은 죄책감을 느끼는 일이 반복되었다. 그가 속한 남부 교회 공동체에서는 환대와 절제가 매우 중요했기 때문에, 그는 대외적으로 보이는 유능한 모습과 사적인 폭식 사이의 괴리에 점점 더 비밀스러워지고 괴로워하게 되었다. 노인복지관에서 열린 섭식 문제에 관한 건강 강연을 듣고 이것이 더 이상 평범한 애도로 인한 식습관이 아니라는 걸 깨달은 후, 그는 스스로 정신건강의학과 진료를 받기로 했다.
+표집된 증상 목록:
+  - S049 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - S050 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+  - S051 급하게 먹기: 평소보다 훨씬 빠르게 먹음.
+  - S052 불편할 정도로 배부르게 먹기: 불편할 정도로 배가 부를 때까지 먹음.
+  - S054 부끄러움으로 인한 혼자 먹기: 먹는 양이 부끄러워 혼자 먹음.
+  - S055 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 폭식장애 (D023) | 중간확률: 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 폭식장애 (D023, ICD: F50.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.; 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode_related (관계=must_include, 요구개수=3, 충족개수=4, 커버리지=1.0)
-  확인된 근거: 급하게 먹기: 평소보다 훨씬 빠르게 먹음.; 불편할 정도로 배부르게 먹기: 불편할 정도로 배가 부를 때까지 먹음.; 부끄러움으로 인한 혼자 먹기: 먹는 양이 부끄러워 혼자 먹음.; 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.
-  누락: 배고프지 않은데 먹기: 신체적으로 배고프지 않은데도 많은 양의 음식을 먹음.</t>
+          <t>의사의 최종 진단: 폭식장애 (D023, ICD: F50.8)
+지속 기간 요건: 없음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+체크리스트 그룹: binge_episode_related (관계=must_include, 요구개수=3, 충족개수=4, 커버리지=1.0)
+확인된 근거:
+  - 급하게 먹기: 평소보다 훨씬 빠르게 먹음.
+  - 불편할 정도로 배부르게 먹기: 불편할 정도로 배가 부를 때까지 먹음.
+  - 부끄러움으로 인한 혼자 먹기: 먹는 양이 부끄러워 혼자 먹음.
+  - 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D023_S002_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S002_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -964,6 +964,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1008,11 +1013,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D023_S002_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S002_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.5263</v>
+        <v>0.8158</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.5263</v>
+        <v>0.8158</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2778</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
